--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2017_T2_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2017_T2_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.264</t>
-  </si>
-  <si>
-    <t>(0.046)</t>
-  </si>
-  <si>
-    <t>0.407</t>
-  </si>
-  <si>
-    <t>(0.052)</t>
-  </si>
-  <si>
-    <t>0.154</t>
-  </si>
-  <si>
-    <t>(0.038)</t>
-  </si>
-  <si>
-    <t>0.615</t>
-  </si>
-  <si>
-    <t>(0.175)</t>
-  </si>
-  <si>
-    <t>0.857</t>
-  </si>
-  <si>
-    <t>(0.153)</t>
-  </si>
-  <si>
-    <t>0.198</t>
-  </si>
-  <si>
-    <t>(0.059)</t>
+    <t>0.276</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>0.425</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>0.161</t>
+  </si>
+  <si>
+    <t>(0.040)</t>
+  </si>
+  <si>
+    <t>0.644</t>
+  </si>
+  <si>
+    <t>(0.183)</t>
+  </si>
+  <si>
+    <t>0.897</t>
+  </si>
+  <si>
+    <t>(0.159)</t>
+  </si>
+  <si>
+    <t>0.207</t>
+  </si>
+  <si>
+    <t>(0.061)</t>
   </si>
   <si>
     <t>23</t>
@@ -135,7 +135,7 @@
     <t>(0.180)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -147,22 +147,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.171</t>
-  </si>
-  <si>
-    <t>0.376***</t>
-  </si>
-  <si>
-    <t>0.368***</t>
-  </si>
-  <si>
-    <t>0.732</t>
-  </si>
-  <si>
-    <t>1.795***</t>
-  </si>
-  <si>
-    <t>0.541***</t>
+    <t>0.159</t>
+  </si>
+  <si>
+    <t>0.357***</t>
+  </si>
+  <si>
+    <t>0.361***</t>
+  </si>
+  <si>
+    <t>0.704</t>
+  </si>
+  <si>
+    <t>1.756***</t>
+  </si>
+  <si>
+    <t>0.532***</t>
   </si>
 </sst>
 </file>
